--- a/Especificaciones del Proyecto de CRM.xlsx
+++ b/Especificaciones del Proyecto de CRM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sistecredito-my.sharepoint.com/personal/julflorez_sistecredito_com/Documents/Escritorio/Especializacion Ingenieria de Software/Gestion de Proyectos/Proyecto de Aula/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{48FC964C-BD43-4902-8F34-9CB24FEFED84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5976065-06F4-40F3-A0F1-E70D142CD17F}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{48FC964C-BD43-4902-8F34-9CB24FEFED84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43DB8157-0C48-4025-A4CC-DCEDBF35BFAE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{143FA800-2352-42A4-951B-BCBF2A659132}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{143FA800-2352-42A4-951B-BCBF2A659132}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>Campo</t>
   </si>
@@ -134,10 +134,49 @@
     <t xml:space="preserve">Objetivos </t>
   </si>
   <si>
-    <t>Ver Documentos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se adjuntan documentos </t>
+    <t>Se adjuntan documentos - Lean Business Case - CRM</t>
+  </si>
+  <si>
+    <t>Analisis de Integraciones</t>
+  </si>
+  <si>
+    <t>Tecnologia</t>
+  </si>
+  <si>
+    <t>Se adjuntan documentos - Alcance de las integraciones</t>
+  </si>
+  <si>
+    <t>Analisis de Gartner</t>
+  </si>
+  <si>
+    <t>Tecnologia - Comercial</t>
+  </si>
+  <si>
+    <t>Se adjuntan documentos - Analisis_de Gartner_CRM</t>
+  </si>
+  <si>
+    <t>Riesgos</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>Se adjuntan documentos - Riesgos CRM Mapa de Calor</t>
+  </si>
+  <si>
+    <t>RACI</t>
+  </si>
+  <si>
+    <t>Se adjuntan documentos - Matriz_RACI_Implementacion_CRM</t>
+  </si>
+  <si>
+    <t>Analisis de RFP</t>
+  </si>
+  <si>
+    <t>Todos</t>
+  </si>
+  <si>
+    <t>Se adjunta documentos - Calificación de proveedores CRM</t>
   </si>
 </sst>
 </file>
@@ -213,9 +252,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -550,16 +587,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C14FE5-61DE-4A46-B0AC-3AEE7E9CD941}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.5703125" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="31.453125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="64.08984375" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -570,7 +607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="28" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -581,7 +618,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -592,18 +629,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -614,7 +651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="28" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -625,69 +662,124 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B14" s="4">
         <v>46296</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B15" s="4">
         <v>46304</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>18</v>
       </c>
     </row>
